--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Заполнение данных</t>
+          <t>Готова к отгрузке</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -576,16 +576,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -642,16 +642,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>для собак фекалии</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>⚠️ пустой короб / нет состава</t>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -660,11 +660,911 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNDEFINED</t>
+          <t>Сортируемый</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>2000063930377</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2000063930377</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2000063930377</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2000063930377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2000063930377</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2000063930378</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2000063930378</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2000063930378</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2000063930378</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2000063930379</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2000063930380</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2000063930380</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2000063930380</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2000063930380</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2000063930380</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2000063930381</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2000063930381</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2000063930381</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2000063930381</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2000063930381</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2000063930381</v>
       </c>
     </row>
   </sheetData>
@@ -678,15 +1578,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,6 +1621,734 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1022100260642000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Краснодар</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1022100266438000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ростов</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1022100266537000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1022100266588000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Готова к отгрузке</t>
+          <t>В пути</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -831,11 +831,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2000063930378</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="8">
@@ -853,25 +853,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2000063930378</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="9">
@@ -889,25 +889,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>для щенков 8в1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2000063930378</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="10">
@@ -925,25 +925,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>для мелких 8в1</t>
+          <t>для щенков 8в1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -952,34 +952,34 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2000063930378</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1022100266438000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>для собак фекалии</t>
+          <t>для мелких 8в1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -988,34 +988,34 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2000063930379</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1022100266438000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2000063930379</v>
+        <v>2000063930381</v>
       </c>
     </row>
     <row r="13">
@@ -1038,16 +1038,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>для собак фекалии</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>для щенков 8в1</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1110,16 +1110,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>для мелких 8в1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>для щенков 8в1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1173,21 +1173,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266438000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>для собак фекалии</t>
+          <t>для мелких 8в1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1204,34 +1204,34 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2000063930380</v>
+        <v>2000063930379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266438000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2000063930380</v>
+        <v>2000063930379</v>
       </c>
     </row>
     <row r="19">
@@ -1249,25 +1249,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>для щенков 8в1</t>
+          <t>для собак фекалии</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2000063930380</v>
+        <v>2000063930378</v>
       </c>
     </row>
     <row r="20">
@@ -1285,25 +1285,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>для мелких 8в1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2000063930380</v>
+        <v>2000063930378</v>
       </c>
     </row>
     <row r="21">
@@ -1321,25 +1321,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>для щенков 8в1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1348,34 +1348,34 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2000063930380</v>
+        <v>2000063930378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1022100266397000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1022100266588000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>для собак фекалии</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>24</v>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2000063930381</v>
+        <v>2000063930378</v>
       </c>
     </row>
     <row r="23">
@@ -1393,25 +1393,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>для собак фекалии</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2000063930381</v>
+        <v>2000063930380</v>
       </c>
     </row>
     <row r="24">
@@ -1429,25 +1429,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2000063930381</v>
+        <v>2000063930380</v>
       </c>
     </row>
     <row r="25">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1479,11 +1479,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2000063930381</v>
+        <v>2000063930380</v>
       </c>
     </row>
     <row r="26">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1515,11 +1515,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2000063930381</v>
+        <v>2000063930380</v>
       </c>
     </row>
     <row r="27">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2000063930381</v>
+        <v>2000063930380</v>
       </c>
     </row>
   </sheetData>
@@ -1661,19 +1661,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1022100266438000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266438000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -1717,19 +1717,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -1773,19 +1773,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -1829,19 +1829,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -1857,19 +1857,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1022100266438000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266438000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -1913,19 +1913,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -2025,19 +2025,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -2053,19 +2053,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -2109,19 +2109,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -2165,19 +2165,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
         <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -2249,19 +2249,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1022100266397000</t>
+          <t>1022100266588000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -2305,19 +2305,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1022100266537000</t>
+          <t>1022100266397000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -2333,19 +2333,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
         <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1022100266588000</t>
+          <t>1022100266537000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>ACCEPTANCE_AT_STORAGE_WAREHOUSE</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/supplies/123761459-1.xlsx
+++ b/supplies/123761459-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
